--- a/papers/References.xlsx
+++ b/papers/References.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\UVSQ\simulation_VLP\papers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\userlisv\Documents\Kevin\Journal simulations\simulation_VLP\papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826F2565-4E9D-4E78-A0EA-C40DE492C819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CE7C90-7287-4FB0-9313-F69F3BCE87F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="80">
   <si>
     <t>Authors</t>
   </si>
@@ -234,11 +234,6 @@
   </si>
   <si>
     <t>Principalmente enfocado en Machine Learning</t>
-  </si>
-  <si>
-    <t>Design and Performance Analysis for Indoor
- Visible Light Positioning With Single LED and
- Single-Tilted-Rotatable PD</t>
   </si>
   <si>
     <t>IEEE Transactions on Instrumentation and Measurement</t>
@@ -280,12 +275,216 @@
 4. Average Position errors : 2.52cm (Simulation)
 5. Real experiments Average position error: 5cm (Experimental)</t>
   </si>
+  <si>
+    <t>Figuras interesante</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fig. 12. Position Performance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Fig 13. CDF of the methods with Average CRLB
+Fig. 14. Comparar errores atraves de SNR.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fig.15. Average Latendy (ms) de cada metodo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fig.18. Distribucion de la potencia por cada orientacion</t>
+    </r>
+  </si>
+  <si>
+    <t>2D
+* 1cm (Mean Position error; pero un testbed de 50cm x 50cm x 30cm )
+* 9.7ms ( latency time of proposed method LS-IGWM)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Describe detalladamente como obtener el CRLB.
+2. Optimiza el angulo de inclinacion (theta) y N.
+3. Trabaja con una varianza conocida (mW) la cual evalua para ver el comportamiento del error 
+4. Las secciones deben ser similares a las que el Journal que se está proponiendo.
+5. Propone inicialmente el LS pero dice que por los NLOS este sera limitado entonces proponer un modelo NO-LINEAL directamente sobre las ecuaciones. Esto los resuelve empleando Swarm-based optimiation algorithm (GWO), donde toma f=|| Pr - Pt||
+6. Añade una SUBSECTION donde discute un caso de fallo, es decir, cuando el LED no esta perfectarmente vertcial, sino que tiene una inclinación y evalua como su método se desempeña ante esta situación.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>7. Comparo diferencias entre el modelo lambertiano y un modelo de ajuste con data : Encontro que mejor se ajusta un modelo de regresion de data en el campo EXPERIMENTAL, por lo que recomienda hacer estos ajustes.</t>
+    </r>
+  </si>
+  <si>
+    <t>Design and Performance Analysis for Indoor Visible Light Positioning With Single LED and Single-Tilted-Rotatable PD</t>
+  </si>
+  <si>
+    <t>Centimeter-Level 3-D Mobile Online Visible Light Positioning System With Single LED Lamp</t>
+  </si>
+  <si>
+    <t>Shuai Ma, Bing Li , Guanjie Zhang, HangLi ,ChenQiu , Chuang Yu, Shiyin Li, Chao Shen</t>
+  </si>
+  <si>
+    <t>Peng Cheng Laboratory, Shenzhen 518055, China
+School of Information and Control Engineering, China University of Mining and Technology, Xuzhou 221116, China
+Department of Industrialization Center, Shenzhen Research Institute of Big Data, Shenzhen 518172, Guangdong, China
+Cognitive Robotics Laboratory, Department of Computer Science, University of Manchester, M13 9PL Manchester, U.K.</t>
+  </si>
+  <si>
+    <t>3D
+(1.77cm APE)</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>Esta más enfocado desde el punto de vista del manejo de data y algoritmos de NN.
+Me quedan dudas respecto a el error porque es bastante bajo.
+Como se obtuvo la distancia geometrica óptima de los PD ??</t>
+  </si>
+  <si>
+    <t>1. Me parece más referencia para un trabajo de MULTI-PD 3D y para DATA-DRIVEN models.
+2. No se explora el CRLB.
+2. ¿Cuál es el Background Noise Filter del que hablan ?</t>
+  </si>
+  <si>
+    <t>3D Single VLP - 4 PD (en una base rectangular)
+Non Linear Least Square (NLS) optimization
+Deep Learning (neural network SGD)
+Data Driven</t>
+  </si>
+  <si>
+    <t>Delineating Regional BES–ELM Neural Networks for Studying
+Indoor Visible Light Positioning</t>
+  </si>
+  <si>
+    <t>Jiaming Zhang and Xizheng Ke</t>
+  </si>
+  <si>
+    <t>Photonics 2024</t>
+  </si>
+  <si>
+    <t>Faculty of Automation and Information Engineering, Xi’an University of Technology, Xi’an 710048, China;
+Shaanxi Provincial Intelligent Collaborative Network Military-Civilian Integration Key Laboratory, Xi’an 710048, China</t>
+  </si>
+  <si>
+    <t>Simulation</t>
+  </si>
+  <si>
+    <t>IEEE Internet of Things Journal</t>
+  </si>
+  <si>
+    <t>Data/Model based?</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Single VLP - 4 PD
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Data-driven</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> algorithm
+Center-Edge Clustering : K-means
+BES-ELM for regression 
+EWKNN + BES-ELM for mejoras</t>
+    </r>
+  </si>
+  <si>
+    <t>Optics Express</t>
+  </si>
+  <si>
+    <t>High accuracy indoor visible light positioning
+using a long short term memory-fully connected
+network based algorithm</t>
+  </si>
+  <si>
+    <t>Shunde Graduate School ofUniversity ofScience and Technology Being, Foshan 528000, China
+School of Computer and Communication Engineering, University ofScience and Technology Beijing, Beijing 100083, China</t>
+  </si>
+  <si>
+    <t>(2.93cm APE)</t>
+  </si>
+  <si>
+    <t>2D
+0.92cm APE</t>
+  </si>
+  <si>
+    <t>Single VLP - 3 PD
+LSTM-FCN</t>
+  </si>
+  <si>
+    <t>Hongyao Chen, Wei Han, Jianping Wang, Huimin Lu, Danyang Chen, Jianli Jin, Lifang Feng</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,6 +502,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
@@ -339,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -364,6 +570,9 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -645,23 +854,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
     <col min="3" max="3" width="24.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="45.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="59.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="42.5703125" style="1" customWidth="1"/>
     <col min="6" max="6" width="94" style="1" customWidth="1"/>
     <col min="7" max="7" width="42.140625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="15" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="113.28515625" style="7" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="8" max="8" width="20.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15" style="1" customWidth="1"/>
+    <col min="10" max="10" width="29.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="113.28515625" style="7" customWidth="1"/>
+    <col min="14" max="14" width="75.140625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
@@ -684,22 +896,28 @@
         <v>4</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>47</v>
+      <c r="M1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>5</v>
       </c>
@@ -721,14 +939,14 @@
       <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="5">
+      <c r="L2" s="5">
         <v>0.4</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="51" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -750,14 +968,14 @@
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="5">
+      <c r="L3" s="5">
         <v>0.8</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -779,14 +997,14 @@
       <c r="G4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="5">
+      <c r="L4" s="5">
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>5</v>
       </c>
@@ -808,23 +1026,23 @@
       <c r="G5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="K5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>50</v>
-      </c>
     </row>
-    <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -846,14 +1064,14 @@
       <c r="G6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -861,32 +1079,149 @@
         <v>2024</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="H7" s="6" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7" s="6"/>
+        <v>52</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" s="9">
+        <v>1</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>77</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>